--- a/Grupo/MDC_Grupo.xlsx
+++ b/Grupo/MDC_Grupo.xlsx
@@ -509,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>4.669999999999999</v>
+        <v>4.67</v>
       </c>
       <c r="C5" s="2">
         <v>109.8849584395483</v>
@@ -518,7 +518,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="2">
-        <v>5.131627559126904</v>
+        <v>5.131627559126905</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="2">
-        <v>5.619999999999998</v>
+        <v>5.62</v>
       </c>
       <c r="C11" s="2">
         <v>127.7714920548454</v>
